--- a/sample-data/Risk Register.xlsx
+++ b/sample-data/Risk Register.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
